--- a/tools/智能车计算器.xlsx
+++ b/tools/智能车计算器.xlsx
@@ -1,25 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e23042d8996ddfe4/桌面/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="11_AD4DA82427541F7ACA7EB8A5188801206BE8DE15" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE34BD50-6CA3-4CD0-A457-36859A991F2F}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="18352" windowHeight="8055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -39,94 +30,415 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>实际电流</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 采样电阻</t>
   </si>
   <si>
     <t>采样电压</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 采样电阻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>增益系数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>输出电压</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ADC读取</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>软件换算后</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编码器线数</t>
+  </si>
+  <si>
+    <t>采样时间</t>
+  </si>
+  <si>
+    <t>编码器实际值</t>
   </si>
   <si>
     <t>齿比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>周长/cm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>t</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>编码器线数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>采样时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>编码器实际值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -136,41 +448,331 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -219,7 +821,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -254,7 +856,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -428,266 +1030,281 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:I11"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B2:J11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
-    <col min="2" max="2" width="11.9296875" customWidth="1"/>
-    <col min="4" max="4" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.929203539823" customWidth="1"/>
+    <col min="4" max="4" width="12.8672566371681" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B2" t="s">
+    <row r="2" spans="2:10">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B3">
+    <row r="3" spans="2:10">
+      <c r="B3" s="1">
         <v>7</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="3">
         <v>10</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <f>C3/1000</f>
         <v>0.01</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <f>B3*D3</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F3" s="1">
+        <v>0.07</v>
+      </c>
+      <c r="F3" s="3">
         <v>20</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <f>F3*E3</f>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="H3">
+        <v>1.4</v>
+      </c>
+      <c r="H3" s="1">
         <f>G3/3.3*4096</f>
         <v>1737.69696969697</v>
       </c>
-      <c r="I3">
-        <f>ABS(H3)/4096*3.3/ F3/D3</f>
-        <v>7.0000000000000009</v>
-      </c>
+      <c r="I3" s="4">
+        <f>ABS(H3)/4096*3.3/F3/D3</f>
+        <v>7</v>
+      </c>
+      <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B4">
+    <row r="4" spans="2:10">
+      <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="3">
         <v>100</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <f t="shared" ref="D4:D6" si="0">C4/1000</f>
         <v>0.1</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <f t="shared" ref="E4:E6" si="1">B4*D4</f>
         <v>0.2</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="3">
         <v>20</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <f t="shared" ref="G4:G6" si="2">F4*E4</f>
         <v>4</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <f t="shared" ref="H4:H6" si="3">G4/3.3*4096</f>
-        <v>4964.848484848485</v>
-      </c>
-      <c r="I4">
-        <f t="shared" ref="I4:I6" si="4">ABS(H4)/4096*3.3/ F4/D4</f>
+        <v>4964.84848484848</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" ref="I4:I6" si="4">ABS(H4)/4096*3.3/F4/D4</f>
         <v>2</v>
       </c>
+      <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B5">
+    <row r="5" spans="2:10">
+      <c r="B5" s="1">
         <v>2</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="3">
         <v>2</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>2E-3</v>
-      </c>
-      <c r="E5">
+        <v>0.002</v>
+      </c>
+      <c r="E5" s="1">
         <f t="shared" si="1"/>
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="F5" s="1">
+        <v>0.004</v>
+      </c>
+      <c r="F5" s="3">
         <v>20</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <f t="shared" si="3"/>
-        <v>99.296969696969711</v>
-      </c>
-      <c r="I5">
+        <v>99.2969696969697</v>
+      </c>
+      <c r="I5" s="4">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
+      <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B6">
+    <row r="6" spans="2:10">
+      <c r="B6" s="1">
         <v>17</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="3">
         <v>2</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <f t="shared" si="0"/>
-        <v>2E-3</v>
-      </c>
-      <c r="E6">
+        <v>0.002</v>
+      </c>
+      <c r="E6" s="1">
         <f t="shared" si="1"/>
-        <v>3.4000000000000002E-2</v>
-      </c>
-      <c r="F6" s="1">
+        <v>0.034</v>
+      </c>
+      <c r="F6" s="3">
         <v>20</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <f t="shared" si="2"/>
         <v>0.68</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <f t="shared" si="3"/>
-        <v>844.02424242424252</v>
-      </c>
-      <c r="I6">
+        <v>844.024242424243</v>
+      </c>
+      <c r="I6" s="4">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
+      <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="C7" s="1">
+    <row r="7" spans="2:10">
+      <c r="B7" s="1"/>
+      <c r="C7" s="3">
         <v>10</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <f t="shared" ref="D7" si="5">C7/1000</f>
         <v>0.01</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <f t="shared" ref="E7" si="6">B7*D7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="3">
         <v>20</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>1.8</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <f t="shared" ref="H7" si="7">G7/3.3*4096</f>
-        <v>2234.1818181818185</v>
-      </c>
-      <c r="I7">
-        <f t="shared" ref="I7" si="8">ABS(H7)/4096*3.3/ F7/D7</f>
+        <v>2234.18181818182</v>
+      </c>
+      <c r="I7" s="4">
+        <f t="shared" ref="I7" si="8">ABS(H7)/4096*3.3/F7/D7</f>
         <v>9</v>
       </c>
+      <c r="J7" s="4"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B9" t="s">
+    <row r="9" spans="2:9">
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="s">
+      <c r="I9" s="1">
+        <f>D10/B10/E10*F10</f>
+        <v>0.301376695793839</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="B10" s="1">
+        <v>512</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1">
+        <v>35</v>
+      </c>
+      <c r="E10" s="1">
+        <v>4.22</v>
+      </c>
+      <c r="F10" s="1">
+        <v>18.6047584</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D9" t="s">
+      <c r="I10" s="1">
+        <f>C11</f>
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1">
+        <f>C10/1000</f>
+        <v>0.003</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9">
-        <f>D10/B10/E10*F10</f>
-        <v>0.30137669579383891</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B10">
-        <v>512</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>35</v>
-      </c>
-      <c r="E10">
-        <v>4.22</v>
-      </c>
-      <c r="F10">
-        <v>18.604758400000001</v>
-      </c>
-      <c r="H10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10">
-        <f>C11</f>
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="C11">
-        <f>C10/1000</f>
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="H11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <f>I9/I10</f>
-        <v>100.4588985979463</v>
+        <v>100.458898597946</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="7">
     <mergeCell ref="C2:D2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>